--- a/app/data/ad_warn_data/Aerodrome_Warnings_Table.xlsx
+++ b/app/data/ad_warn_data/Aerodrome_Warnings_Table.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aerodrome Warnings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Aerodrome Warnings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/app/data/ad_warn_data/Aerodrome_Warnings_Table.xlsx
+++ b/app/data/ad_warn_data/Aerodrome_Warnings_Table.xlsx
@@ -442,7 +442,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Aerodrome warning for station VABB for June 2025</t>
+          <t>Aerodrome warning for station VABB for September 2025</t>
         </is>
       </c>
     </row>
@@ -513,12 +513,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>02/2030,03/0030,03/1700,04/0415,04/0830,11/2000,12/0900,12/2130,13/0300,13/1245,13/1645,13/2030,14/2015,15/0015,15/0845,15/1230,15/1645,15/2030,16/0130,16/0300,16/1030,16/1430,16/1830,16/2230,17/1830,18/0630,18/1400,18/1800,18/2200,19/0200,19/0600,19/1400,20/0600,20/1000,20/1400,23/0000,23/0000,27/0030,28/1350,28/1830</t>
+          <t>04/0330,04/0730,13/0800,13/1230,13/1845,14/1600,14/2000,15/0000,15/0400,15/0800,16/0830,18/1030,18/1900,18/2300,19/0900,20/1645,21/0130,21/0800,21/1200,21/1600,21/2130,22/0130,22/0530,22/1400,23/0030,26/1100,27/0130,27/0530,27/0930,27/1330,27/1730,27/2130,28/0130,28/0530,28/0930,28/1330,28/2130</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -730,12 +730,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>01/0330,01/0730,01/1145,01/1600,01/2015,02/0215,02/0600,02/1015,02/1400,02/2030,03/0030,03/0430,03/0830,03/1230,04/0330,04/0830,05/0830,06/0545,06/1000,08/0830,09/0430,09/0830,11/0645,12/0500,12/0900,12/1730,14/1230,14/1615,14/2015,15/0015,15/0845,15/2315,16/0300,16/0930,16/1030,16/1430,16/1830,16/2230,17/0230,17/0630,17/1030,17/1500,17/1830,17/2230,17/2230,18/0230,18/0630,18/1115,18/1500,18/1800,18/2200,19/0200,19/0600,19/1400,19/2200,20/0200,20/0600,20/1000,20/1400,20/1800,20/2200,21/0200,21/0600,21/1000,21/1400,21/1800,21/2200,23/0000,23/0400,23/0800,23/1200,23/1600,23/2000,23/0000,23/0400,23/0800,23/1200,23/1600,23/2000,24/0000,24/0400,24/1600,24/2000,27/0030,27/0430,27/0830,27/1230,27/1715,27/2100,28/0100,28/0500,28/0620,28/0950,28/1350,28/1830,29/0015,29/0415,29/1215,29/1615,29/2015,30/0015,30/0415,30/1230,30/1630,30/2030</t>
+          <t>01/0000,01/0400,01/0800,01/1430,01/1830,01/2030,02/0030,02/0430,02/0830,02/1230,02/1630,02/2030,03/0030,03/0530,03/0930,04/0330,04/0730,04/2000,05/0300,05/0730,05/1645,05/2045,06/0100,06/0830,06/1515,06/1945,07/0000,07/0400,07/0800,08/0240,08/0645,08/1045,09/0400,09/0800,11/0830,12/1130,13/0800,13/1230,13/1845,14/1600,14/2000,15/0000,15/0400,15/0800,16/0830,18/1030,18/1900,18/2300,19/0900,20/0930,21/0800,21/1200,21/1600,24/1000,25/0600,26/1100,27/0130,27/1330,27/1730,27/2130,28/0130,28/0530,28/0930,28/1330,28/1730,28/2130,29/0130,29/0530,29/1030,29/1630,29/2000,30/0100,30/0500,30/0900,30/1300,30/1700</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
